--- a/NIK NOP PLK.xlsx
+++ b/NIK NOP PLK.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22400" windowHeight="11230"/>
+    <workbookView windowWidth="19200" windowHeight="7760"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="95">
   <si>
     <t>NAMA</t>
   </si>
@@ -309,6 +309,9 @@
   </si>
   <si>
     <t>B09252503</t>
+  </si>
+  <si>
+    <t>IRJAN TORO</t>
   </si>
 </sst>
 </file>
@@ -316,10 +319,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -815,16 +818,16 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1492,7 +1495,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B47"/>
+  <dimension ref="A1:B48"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="12.3636363636364" customWidth="1"/>
@@ -1507,7 +1510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" ht="62.75" spans="1:2">
+    <row r="2" ht="31.75" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1515,7 +1518,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" ht="31.75" spans="1:2">
+    <row r="3" ht="16.25" spans="1:2">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1523,7 +1526,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" ht="62.75" spans="1:2">
+    <row r="4" ht="31.75" spans="1:2">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1531,7 +1534,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" ht="47.25" spans="1:2">
+    <row r="5" ht="31.75" spans="1:2">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -1539,7 +1542,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" ht="47.25" spans="1:2">
+    <row r="6" ht="31.75" spans="1:2">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -1547,7 +1550,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" ht="31.75" spans="1:2">
+    <row r="7" ht="16.25" spans="1:2">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
@@ -1555,7 +1558,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" ht="31.75" spans="1:2">
+    <row r="8" ht="16.25" spans="1:2">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -1563,7 +1566,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" ht="47.25" spans="1:2">
+    <row r="9" ht="31.75" spans="1:2">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
@@ -1571,7 +1574,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" ht="47.25" spans="1:2">
+    <row r="10" ht="31.75" spans="1:2">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -1579,7 +1582,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" ht="31.75" spans="1:2">
+    <row r="11" ht="16.25" spans="1:2">
       <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
@@ -1587,7 +1590,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" ht="31.75" spans="1:2">
+    <row r="12" ht="16.25" spans="1:2">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
@@ -1595,7 +1598,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" ht="47.25" spans="1:2">
+    <row r="13" ht="31.75" spans="1:2">
       <c r="A13" s="2" t="s">
         <v>24</v>
       </c>
@@ -1603,7 +1606,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" ht="78.25" spans="1:2">
+    <row r="14" ht="47.25" spans="1:2">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
@@ -1611,7 +1614,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" ht="47.25" spans="1:2">
+    <row r="15" ht="31.75" spans="1:2">
       <c r="A15" s="2" t="s">
         <v>28</v>
       </c>
@@ -1619,7 +1622,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" ht="47.25" spans="1:2">
+    <row r="16" ht="31.75" spans="1:2">
       <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
@@ -1627,7 +1630,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" ht="31.75" spans="1:2">
+    <row r="17" ht="16.25" spans="1:2">
       <c r="A17" s="2" t="s">
         <v>32</v>
       </c>
@@ -1635,7 +1638,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" ht="62.75" spans="1:2">
+    <row r="18" ht="47.25" spans="1:2">
       <c r="A18" s="1" t="s">
         <v>34</v>
       </c>
@@ -1643,7 +1646,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" ht="31.75" spans="1:2">
+    <row r="19" ht="16.25" spans="1:2">
       <c r="A19" s="2" t="s">
         <v>36</v>
       </c>
@@ -1667,7 +1670,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" ht="47.25" spans="1:2">
+    <row r="22" ht="31.75" spans="1:2">
       <c r="A22" s="1" t="s">
         <v>42</v>
       </c>
@@ -1675,7 +1678,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" ht="31.75" spans="1:2">
+    <row r="23" ht="16.25" spans="1:2">
       <c r="A23" s="2" t="s">
         <v>44</v>
       </c>
@@ -1683,7 +1686,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" ht="31.75" spans="1:2">
+    <row r="24" ht="16.25" spans="1:2">
       <c r="A24" s="1" t="s">
         <v>46</v>
       </c>
@@ -1699,7 +1702,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" ht="93.75" spans="1:2">
+    <row r="26" ht="62.75" spans="1:2">
       <c r="A26" s="1" t="s">
         <v>50</v>
       </c>
@@ -1707,7 +1710,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" ht="62.75" spans="1:2">
+    <row r="27" ht="31.75" spans="1:2">
       <c r="A27" s="2" t="s">
         <v>52</v>
       </c>
@@ -1715,7 +1718,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" ht="47.25" spans="1:2">
+    <row r="28" ht="31.75" spans="1:2">
       <c r="A28" s="1" t="s">
         <v>54</v>
       </c>
@@ -1723,7 +1726,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" ht="47.25" spans="1:2">
+    <row r="29" ht="31.75" spans="1:2">
       <c r="A29" s="2" t="s">
         <v>56</v>
       </c>
@@ -1731,7 +1734,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" ht="47.25" spans="1:2">
+    <row r="30" ht="31.75" spans="1:2">
       <c r="A30" s="1" t="s">
         <v>58</v>
       </c>
@@ -1739,7 +1742,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" ht="31.75" spans="1:2">
+    <row r="31" ht="16.25" spans="1:2">
       <c r="A31" s="2" t="s">
         <v>60</v>
       </c>
@@ -1747,7 +1750,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" ht="31.75" spans="1:2">
+    <row r="32" ht="16.25" spans="1:2">
       <c r="A32" s="1" t="s">
         <v>62</v>
       </c>
@@ -1779,7 +1782,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36" ht="31.75" spans="1:2">
+    <row r="36" ht="16.25" spans="1:2">
       <c r="A36" s="1" t="s">
         <v>70</v>
       </c>
@@ -1787,7 +1790,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" ht="47.25" spans="1:2">
+    <row r="37" ht="31.75" spans="1:2">
       <c r="A37" s="2" t="s">
         <v>72</v>
       </c>
@@ -1795,7 +1798,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="38" ht="62.75" spans="1:2">
+    <row r="38" ht="47.25" spans="1:2">
       <c r="A38" s="1" t="s">
         <v>74</v>
       </c>
@@ -1811,7 +1814,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="40" ht="31.75" spans="1:2">
+    <row r="40" ht="16.25" spans="1:2">
       <c r="A40" s="1" t="s">
         <v>78</v>
       </c>
@@ -1819,7 +1822,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" ht="31.75" spans="1:2">
+    <row r="41" ht="16.25" spans="1:2">
       <c r="A41" s="2" t="s">
         <v>80</v>
       </c>
@@ -1827,7 +1830,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="42" ht="47.25" spans="1:2">
+    <row r="42" ht="31.75" spans="1:2">
       <c r="A42" s="1" t="s">
         <v>82</v>
       </c>
@@ -1835,7 +1838,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="43" ht="31.75" spans="1:2">
+    <row r="43" ht="16.25" spans="1:2">
       <c r="A43" s="2" t="s">
         <v>84</v>
       </c>
@@ -1843,7 +1846,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="44" ht="31.75" spans="1:2">
+    <row r="44" ht="16.25" spans="1:2">
       <c r="A44" s="1" t="s">
         <v>86</v>
       </c>
@@ -1851,7 +1854,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="45" ht="31.75" spans="1:2">
+    <row r="45" ht="16.25" spans="1:2">
       <c r="A45" s="2" t="s">
         <v>88</v>
       </c>
@@ -1859,7 +1862,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="46" ht="47.25" spans="1:2">
+    <row r="46" ht="31.75" spans="1:2">
       <c r="A46" s="1" t="s">
         <v>90</v>
       </c>
@@ -1867,11 +1870,19 @@
         <v>91</v>
       </c>
     </row>
-    <row r="47" ht="47.25" spans="1:2">
+    <row r="47" ht="31.75" spans="1:2">
       <c r="A47" s="2" t="s">
         <v>92</v>
       </c>
       <c r="B47" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="48" ht="31.75" spans="1:2">
+      <c r="A48" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>93</v>
       </c>
     </row>

--- a/NIK NOP PLK.xlsx
+++ b/NIK NOP PLK.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7760"/>
+    <workbookView windowWidth="19200" windowHeight="8000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="96">
   <si>
     <t>NAMA</t>
   </si>
@@ -312,6 +312,9 @@
   </si>
   <si>
     <t>IRJAN TORO</t>
+  </si>
+  <si>
+    <t>RIO ARDINAT</t>
   </si>
 </sst>
 </file>
@@ -1495,7 +1498,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B48"/>
+  <dimension ref="A1:B49"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="12.3636363636364" customWidth="1"/>
@@ -1878,11 +1881,19 @@
         <v>93</v>
       </c>
     </row>
-    <row r="48" ht="31.75" spans="1:2">
+    <row r="48" ht="16.25" spans="1:2">
       <c r="A48" s="2" t="s">
         <v>94</v>
       </c>
       <c r="B48" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="49" ht="16.25" spans="1:2">
+      <c r="A49" t="s">
+        <v>95</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>93</v>
       </c>
     </row>
